--- a/Інтелектуальний аналіз даних/Goretsky_lab3-4.xlsx
+++ b/Інтелектуальний аналіз даних/Goretsky_lab3-4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\edu\education\Інтелектуальний аналіз даних\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641C1781-FBB1-48FC-BD1B-6A2309DE2275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F981EA3-9E97-44A6-94B0-94ED114E9A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1644" yWindow="2580" windowWidth="20520" windowHeight="9960" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Колективна 1 - постановк" sheetId="1" r:id="rId1"/>
@@ -216,6 +216,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -227,9 +230,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -302,16 +302,25 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'колективна 1 - розв''язання'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -331,6 +340,65 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'колективна 1 - розв''язання'!$A$2:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
           <c:yVal>
             <c:numRef>
               <c:f>'колективна 1 - розв''язання'!$B$2:$B$13</c:f>
@@ -376,10 +444,10 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C972-4961-8A9C-8B7B71D46B22}"/>
+              <c16:uniqueId val="{00000000-44A0-4740-9377-0C85F0D810AD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -391,11 +459,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="914513919"/>
-        <c:axId val="914514335"/>
+        <c:axId val="415903888"/>
+        <c:axId val="415905136"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="914513919"/>
+        <c:axId val="415903888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -415,6 +483,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -451,12 +520,12 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="914514335"/>
+        <c:crossAx val="415905136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="914514335"/>
+        <c:axId val="415905136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -513,7 +582,7 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="914513919"/>
+        <c:crossAx val="415903888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1129,23 +1198,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Діаграма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD2DB9E4-926B-4E6A-847F-98ACD57BE1E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{300AA22F-D1CC-44BF-819A-EE1ECFF6A3A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1437,25 +1506,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1540,18 +1609,18 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1850,6 +1919,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1859,7 +1929,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1877,114 +1946,114 @@
       <c r="A3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
-      <c r="B4" s="7">
+      <c r="B4" s="3">
         <v>10</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="3">
         <v>12</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>13</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="3">
         <v>14</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="3">
         <v>15</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>5</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>3</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+      <c r="A6" s="3">
         <v>10</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3">
         <v>7</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>15</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
         <v>2</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>5</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="3">
         <v>2</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+      <c r="A8" s="3">
         <v>20</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
         <v>1</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="3">
         <v>10</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+      <c r="A9" s="3">
         <v>25</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
         <v>4</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="3">
         <v>7</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="3">
         <v>3</v>
       </c>
     </row>
@@ -2006,114 +2075,114 @@
       <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>10</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>12</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="3">
         <v>13</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="3">
         <v>14</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="3">
         <v>15</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
+      <c r="A3" s="3">
         <v>5</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>2</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>3</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="A4" s="3">
         <v>10</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3">
         <v>7</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>15</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="3">
         <v>5</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+      <c r="A6" s="3">
         <v>20</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="3">
         <v>10</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>25</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
         <v>4</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="3">
         <v>7</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="3">
         <v>3</v>
       </c>
     </row>
